--- a/SmartKisan_Feature_List.xlsx
+++ b/SmartKisan_Feature_List.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$4:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$4:$H$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2260,42 +2260,42 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="n">
+      <c r="A49" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Farm</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>Crop growth trends</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>How crops are growing over the season.</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>FarmManagement</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>Sample data, no server</t>
-        </is>
-      </c>
-      <c r="G49" s="8" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>Left empty on purpose. Needs a season of recorded measurements that nothing collects yet; a made-up curve would be worse than none.</t>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Record a harvest</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>What actually came off each field - quantity, area, quality and what was expected.</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Harvests, RecordHarvestModal</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Server (real farm data)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Accepts quintals, kilograms, tonnes or maunds over acres, bigha or hectares, and works out yield per acre so seasons can be compared. Choosing a crop already sown fills in its field and area.</t>
         </is>
       </c>
     </row>
@@ -2305,22 +2305,22 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Farm</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Device list and detail</t>
+          <t>Yield history</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Sensors and controllers on the farm, and whether they are online.</t>
+          <t>Average, best and worst yield per acre for each crop, and how the last harvest compared.</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>DeviceList, DeviceDetail, ConnectedDevices</t>
+          <t>Harvests</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2333,45 +2333,49 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>A comparison only appears after a second season of that crop - there is no average to be above or below before then.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n">
+      <c r="A51" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Connect a device</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Pair a new sensor or controller.</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>DeviceConnection</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Server (real farm data)</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>No physical hardware built yet - tested with simulated devices.</t>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Farm</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Crop growth trends</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>How crops are growing over the season.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>FarmManagement</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>Sample data, no server</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>Left empty on purpose. Needs a season of recorded measurements that nothing collects yet; a made-up curve would be worse than none.</t>
         </is>
       </c>
     </row>
@@ -2386,17 +2390,17 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Calibrate a sensor</t>
+          <t>Device list and detail</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Step-by-step sensor calibration.</t>
+          <t>Sensors and controllers on the farm, and whether they are online.</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CalibrationWizard</t>
+          <t>DeviceList, DeviceDetail, ConnectedDevices</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2422,17 +2426,17 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Alert rules</t>
+          <t>Connect a device</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Be told when a reading crosses a limit.</t>
+          <t>Pair a new sensor or controller.</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>AlertRules, AddAlertRule</t>
+          <t>DeviceConnection</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2445,7 +2449,11 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>No physical hardware built yet - tested with simulated devices.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2453,22 +2461,22 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Water, hours and energy</t>
+          <t>Calibrate a sensor</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>How much water and electricity the farm used, and for how long the pumps ran, by day and by week.</t>
+          <t>Step-by-step sensor calibration.</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>ComprehensiveReport, MetricReports, TrendReports</t>
+          <t>CalibrationWizard</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2481,11 +2489,7 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>Worked out from recorded pump runs: litres from each pump's flow rate, units from its horsepower. Compares against the period before.</t>
-        </is>
-      </c>
+      <c r="H54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2493,77 +2497,73 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Alert rules</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Be told when a reading crosses a limit.</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>AlertRules, AddAlertRule</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Server (real farm data)</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
           <t>Reports</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Soil condition report</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>Moisture, pH and nutrients rated in plain words.</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>SoilHarvestReport</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Water, hours and energy</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>How much water and electricity the farm used, and for how long the pumps ran, by day and by week.</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>ComprehensiveReport, MetricReports, TrendReports</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Server (real farm data)</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Rated against Soil Health Card bands. The nutrient rating takes the worst of N, P and K, not the average - a farmer acts on the one that is short.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>Harvest performance</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>Expected against actual yield.</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>SoilHarvestReport</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>Sample data, no server</t>
-        </is>
-      </c>
-      <c r="G56" s="8" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>Left empty on purpose. Nothing records a sowing or a harvest, so there is no yield to compare. It used to show 91.7% efficiency to everyone.</t>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Worked out from recorded pump runs: litres from each pump's flow rate, units from its horsepower. Compares against the period before.</t>
         </is>
       </c>
     </row>
@@ -2573,27 +2573,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Analytics</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Crop health</t>
+          <t>Soil condition report</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A health score per field, with what is wrong listed.</t>
+          <t>Moisture, pH and nutrients rated in plain words.</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>FarmAnalytics, FarmOverview</t>
+          <t>SoilHarvestReport</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Calculated in the app</t>
+          <t>Server (real farm data)</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Scored from the farm's soil reading against Soil Health Card bands. A field with no reading shows as unknown rather than being given a number.</t>
+          <t>Rated against Soil Health Card bands. The nutrient rating takes the worst of N, P and K, not the average - a farmer acts on the one that is short.</t>
         </is>
       </c>
     </row>
@@ -2613,117 +2613,117 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Harvest performance</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Expected against actual yield.</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>SoilHarvestReport</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Server (real farm data)</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Real once a harvest is recorded. Efficiency is worked out only from records that carry an expectation, and the count of those is shown, so a missing expectation is not quietly treated as a met one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
           <t>Analytics</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Crop health</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>A health score per field, with what is wrong listed.</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>FarmAnalytics, FarmOverview</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Calculated in the app</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Scored from the farm's soil reading against Soil Health Card bands. A field with no reading shows as unknown rather than being given a number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Farm observations</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Plain advice drawn from the readings - dry soil, short nutrients, a pump offline, a harvest coming up.</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>FarmAnalytics</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Calculated in the app</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>Each one says which reading it came from. Dry soil with rain forecast says wait rather than irrigate. No readings means no advice, instead of four cheerful tips.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Expert network</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>Agronomists a farmer can consult.</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>FarmAnalytics</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>Sample data, no server</t>
-        </is>
-      </c>
-      <c r="G59" s="8" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>Removed. These were invented names with invented ratings; a farmer ringing one would find nobody. Needs real agronomists signed up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Analytics</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Satellite crop health (NDVI)</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>Crop health from satellite imagery.</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>NDVIMap</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>Sample data, no server</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>Returns nothing now rather than a made-up index. Needs a satellite imagery provider - Sentinel-2 through Copernicus is free but needs an account and real work to wire up.</t>
         </is>
       </c>
     </row>
@@ -2738,17 +2738,17 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Yield prediction</t>
+          <t>Expert network</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Expected harvest.</t>
+          <t>Agronomists a farmer can consult.</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>YieldPrediction</t>
+          <t>FarmAnalytics</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Returns nothing now rather than a made-up figure. Needs a season of recorded harvests first, which means recording sowings and harvests - a feature in itself, and the sensible next thing to build.</t>
+          <t>Removed. These were invented names with invented ratings; a farmer ringing one would find nobody. Needs real agronomists signed up.</t>
         </is>
       </c>
     </row>
@@ -2773,157 +2773,157 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Satellite crop health (NDVI)</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>Crop health from satellite imagery.</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>NDVIMap</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>Sample data, no server</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Returns nothing now rather than a made-up index. Needs a satellite imagery provider - Sentinel-2 through Copernicus is free but needs an account and real work to wire up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Yield prediction</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Expected harvest for each crop in the ground.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>YieldPrediction</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Calculated in the app</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>The farmer's own average yield per acre over the area planted, with the arithmetic shown. Not a trained model and not described as one. It will not predict a crop it has never seen harvested.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>Buy and sell produce</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Listings, chat with buyers, and creating a listing.</t>
         </is>
       </c>
-      <c r="E62" s="7" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>MarketplaceHome, ListingDetail, CreateListing, ChatList, Chat</t>
         </is>
       </c>
-      <c r="F62" s="7" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Sample data, no server</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>Work in progress</t>
         </is>
       </c>
-      <c r="H62" s="7" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>The largest of the unfinished features: needs buyers, sellers, messaging and payments.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>Mandi prices</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>Market prices for crops.</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>MandiPrices</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Sample data, no server</t>
         </is>
       </c>
-      <c r="G63" s="9" t="inlineStr">
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>Work in progress</t>
         </is>
       </c>
-      <c r="H63" s="7" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>The government publishes daily mandi prices through data.gov.in and this could use them. The feed did not respond when tried, so it needs our own free API key from data.gov.in before it can be wired and tested.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Schemes</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Government schemes</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>PM-KISAN, Fasal Bima, KCC, Soil Health Card, eNAM and others, with eligibility and how to apply.</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>GovernmentSchemes, SchemeDetail</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Built into the app</t>
-        </is>
-      </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>Real schemes, stored in the app rather than fetched. Needs someone to keep the details current.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>My profile</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Change name, phone, farm name and farm location.</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>UserProfile</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Server (real farm data)</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Opened blank and saved nothing before; both fixed.</t>
         </is>
       </c>
     </row>
@@ -2933,27 +2933,27 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Schemes</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Notification settings</t>
+          <t>Government schemes</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Choose which alerts to receive.</t>
+          <t>PM-KISAN, Fasal Bima, KCC, Soil Health Card, eNAM and others, with eligibility and how to apply.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>NotificationSettings</t>
+          <t>GovernmentSchemes, SchemeDetail</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Server (real farm data)</t>
+          <t>Built into the app</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -2961,7 +2961,11 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H66" s="4" t="inlineStr"/>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Real schemes, stored in the app rather than fetched. Needs someone to keep the details current.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -2974,17 +2978,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>App settings</t>
+          <t>My profile</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Language, units and location.</t>
+          <t>Change name, phone, farm name and farm location.</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>SettingsMain, SettingsDetail</t>
+          <t>UserProfile</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2997,7 +3001,11 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr"/>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Opened blank and saved nothing before; both fixed.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -3005,27 +3013,27 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Across the app</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Works offline</t>
+          <t>Notification settings</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Recently loaded data stays readable with no signal, and the app says when it is offline.</t>
+          <t>Choose which alerts to receive.</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>NotificationSettings</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Calculated in the app</t>
+          <t>Server (real farm data)</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -3033,11 +3041,7 @@
           <t>Working</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>Actions needing the server are refused clearly rather than failing silently.</t>
-        </is>
-      </c>
+      <c r="H68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -3045,42 +3049,238 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>App settings</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Language, units and location.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>SettingsMain, SettingsDetail</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Server (real farm data)</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>Across the app</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Read aloud</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Reads the advice out in the farmer's own language - the disease diagnosis and treatment, the weed result, farm observations and weather warnings.</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Disease, Weed, Analytics, Weather</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Calculated in the app</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Uses the phone's own voice, so it works without a connection once the language pack is installed. The button hides itself when the phone has no voice for that language rather than playing silence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Across the app</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Speak to move around</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Say what you want and the app opens it - weather, soil, pumps, harvests, schemes and the rest.</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Home (microphone)</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Calculated in the app</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Hindi, Punjabi and English; the recogniser handles the other seven poorly. It navigates and never writes to a record: a misheard screen name is visible and correctable, a misheard quantity would not be. 43 spoken phrases are checked by npm run check:voice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Spray and weather warnings</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Which days are fit to spray and why not on the others, plus heat, frost and heavy-rain warnings with the day named.</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>WeatherToday</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Weather service</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Worked out from wind and expected rainfall. Each carries the forecast figure it came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Across the app</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Works offline</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Recently loaded data stays readable with no signal, and the app says when it is offline.</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Calculated in the app</t>
+        </is>
+      </c>
+      <c r="G73" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Actions needing the server are refused clearly rather than failing silently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Across the app</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Live updates</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Pump state and sensor readings update without refreshing.</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Pumps, Soil, Devices</t>
         </is>
       </c>
-      <c r="F69" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>Sensors over MQTT</t>
         </is>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>Working</t>
-        </is>
-      </c>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
+        <is>
+          <t>Working</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>Runs on a public message broker. Anyone knowing a farmer's ID could read their sensors or switch their pump - must move to a private broker before real farms use it.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H69"/>
+  <autoFilter ref="A4:H74"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -3134,7 +3334,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
@@ -3179,7 +3379,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -3194,7 +3394,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" t="inlineStr"/>
     </row>
@@ -3236,12 +3436,12 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Dashboard</t>
+          <t>Weather</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>5 of 5 working</t>
+          <t>6 of 6 working</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr"/>
@@ -3249,7 +3449,7 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Weather</t>
+          <t>Dashboard</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
@@ -3267,7 +3467,7 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>2 of 5 working</t>
+          <t>3 of 5 working</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr"/>
@@ -3301,12 +3501,12 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Devices</t>
+          <t>Farm</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>4 of 4 working</t>
+          <t>3 of 4 working</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr"/>
@@ -3314,12 +3514,12 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Devices</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>3 of 3 working</t>
+          <t>4 of 4 working</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr"/>
@@ -3327,12 +3527,12 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Crops &amp; Fields</t>
+          <t>Across the app</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>3 of 3 working</t>
+          <t>4 of 4 working</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr"/>
@@ -3340,12 +3540,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Reports</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>2 of 3 working</t>
+          <t>3 of 3 working</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr"/>
@@ -3353,7 +3553,7 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Crops &amp; Fields</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -3366,12 +3566,12 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>Farm</t>
+          <t>Reports</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>1 of 2 working</t>
+          <t>3 of 3 working</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr"/>
@@ -3379,12 +3579,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>0 of 2 working</t>
+          <t>3 of 3 working</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr"/>
@@ -3392,12 +3592,12 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>Across the app</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>2 of 2 working</t>
+          <t>0 of 2 working</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr"/>
